--- a/docentes/Hernández Castro Enrique - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Castro Enrique - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -91,31 +91,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
   </si>
 </sst>
 </file>
@@ -763,16 +754,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -786,16 +780,19 @@
         <v>29</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>29</v>
       </c>
-      <c r="E3">
-        <v>29</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -809,16 +806,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.62</v>
+      </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -832,16 +832,19 @@
         <v>35</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>35</v>
       </c>
-      <c r="E5">
-        <v>35</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -855,16 +858,19 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.67</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -878,16 +884,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -901,16 +910,19 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H8">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -924,16 +936,19 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H9">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -989,16 +1004,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1015,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1050,7 +1065,7 @@
         <v>97.62</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1067,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>91.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1093,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>95.56</v>
+        <v>86.67</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1119,16 +1134,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1145,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>92.11</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H8">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1171,16 +1186,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G9">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H9">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1222,16 +1237,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920218</v>
+        <v>22330051920064</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1245,71 +1260,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920176</v>
+        <v>22330051920068</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920176</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920144</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Castro Enrique - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Castro Enrique - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -89,24 +89,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
   </si>
 </sst>
 </file>
@@ -1004,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1039,7 +1021,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1091,7 +1073,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1108,16 +1090,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G6">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1134,16 +1116,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>87.09999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1169,7 +1151,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H8">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1195,7 +1177,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H9">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1235,52 +1217,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920064</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920068</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
